--- a/hira_material_automation/output/monthly/202601_202605__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -431,7 +431,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -486,7 +486,11 @@
           <t>040023</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>십자인대고정용 일차 고정재 - SCREW,BUTTON 등(금속류)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>1249</t>
@@ -519,7 +523,11 @@
           <t>040023</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>십자인대고정용 일차 고정재 - SCREW,BUTTON 등(금속류)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>1081</t>
@@ -552,7 +560,11 @@
           <t>040023</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>십자인대고정용 일차 고정재 - SCREW,BUTTON 등(금속류)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>1155</t>
@@ -625,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-04T22:06:58</t>
+          <t>2026-05-14T22:15:12</t>
         </is>
       </c>
     </row>
@@ -637,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2dcbe0a63bd4ebf602049cba275039d1dd9afb08eb86b6ad361fc30bd6210971</t>
+          <t>ac9608446b8a272a6f3d45b1572d2f027641e8f215e401513e1a56fc8c4de793</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202605__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202605__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-14T22:15:12</t>
+          <t>2026-05-24T21:59:49</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ac9608446b8a272a6f3d45b1572d2f027641e8f215e401513e1a56fc8c4de793</t>
+          <t>786c26cd22f0d2135ed53d06ea5184ac3647d8f23a9472236a8168137fc55d70</t>
         </is>
       </c>
     </row>
